--- a/product-definitions/spreadsheet/precipitation.xlsx
+++ b/product-definitions/spreadsheet/precipitation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="96">
   <si>
     <t>Name</t>
   </si>
@@ -36,13 +36,13 @@
     <t>measurement_technique</t>
   </si>
   <si>
-    <t>optical, peizoelectric, tipping_bucket, drop_counting, weighing, collecting, droplet_impact</t>
+    <t>optical, piezoelectric, tipping_bucket, drop_counting, weighing, collecting, droplet_impact</t>
   </si>
   <si>
     <t>drop_counting</t>
   </si>
   <si>
-    <t>One of: optical, peizoelectric, tipping_bucket, drop_counting, weighing, collecting, droplet_impact</t>
+    <t>One of: optical, piezoelectric, tipping_bucket, drop_counting, weighing, collecting, droplet_impact</t>
   </si>
   <si>
     <t>measurement_quanta</t>
@@ -174,7 +174,7 @@
     <t>time, fallspeed, diameter</t>
   </si>
   <si>
-    <t>Number of Hydrometeors per Instrument Channel</t>
+    <t>Number of Hydrometeors per Fallspeed Channel per Instrument Channel</t>
   </si>
   <si>
     <t>&lt;derived from file&gt;</t>
@@ -186,7 +186,7 @@
     <t>time: mean</t>
   </si>
   <si>
-    <t>number_of_hydrometeor_per_size_channel</t>
+    <t>number_of_hydrometeors_per_size_channel</t>
   </si>
   <si>
     <t>time, diameter</t>
@@ -258,6 +258,9 @@
     <t>number_of_drops</t>
   </si>
   <si>
+    <t>int32</t>
+  </si>
+  <si>
     <t xml:space="preserve">Number of Pulses\Drops Counted in Integration Period </t>
   </si>
   <si>
@@ -300,9 +303,9 @@
     <t>not_used
 good_data 
 instrument_error
-bad_data_precipitation_rate_&lt;_0_mm_hr-1
-suspect_data_precipitation_rate_&gt;_300_mm_hr-1
-suspect_data_solid_precipitation_rate_&gt;_300_mm_hr-1</t>
+bad_data_precipitation_rate_less_than_0_mm_hr-1
+suspect_data_precipitation_rate_greater_than_300_mm_hr-1
+suspect_data_solid_precipitation_rate_greater_than_300_mm_hr-1</t>
   </si>
 </sst>
 </file>
@@ -313,7 +316,8 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -334,14 +338,16 @@
       <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -382,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -401,48 +407,38 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
@@ -450,38 +446,28 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,11 +744,11 @@
       <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="4"/>
@@ -788,17 +774,17 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="4"/>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="4"/>
@@ -824,17 +810,17 @@
       <c r="Z3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="4"/>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="4"/>
@@ -866,11 +852,11 @@
       <c r="B5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="4"/>
@@ -896,17 +882,17 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="4"/>
@@ -934,7 +920,7 @@
     <row r="7">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="8"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -962,7 +948,7 @@
     <row r="8">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="8"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -7675,6 +7661,7 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -7694,75 +7681,75 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
     </row>
     <row r="2" ht="12.0" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>22.0</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
     </row>
     <row r="3" ht="12.0" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="13">
         <v>20.0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -8784,2026 +8771,2026 @@
     <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.0" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1">
+      <c r="A1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" ht="12.0" customHeight="1">
-      <c r="A2" s="18" t="s">
+    <row r="2">
+      <c r="A2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-    </row>
-    <row r="3" ht="12.0" customHeight="1">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-    </row>
-    <row r="4" ht="12.0" customHeight="1">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-    </row>
-    <row r="5" ht="12.0" customHeight="1">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-    </row>
-    <row r="6" ht="12.0" customHeight="1">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="19"/>
-    </row>
-    <row r="7" ht="12.0" customHeight="1">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19" t="s">
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-    </row>
-    <row r="8" ht="12.0" customHeight="1">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="18">
         <v>-1.0E20</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-    </row>
-    <row r="9" ht="12.0" customHeight="1">
-      <c r="A9" s="19"/>
-      <c r="B9" s="22" t="s">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16"/>
+      <c r="B9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="19"/>
-    </row>
-    <row r="10" ht="12.0" customHeight="1">
-      <c r="A10" s="19"/>
-      <c r="B10" s="22" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="19"/>
-    </row>
-    <row r="11" ht="12.0" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-    </row>
-    <row r="12" ht="12.0" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-    </row>
-    <row r="13" ht="12.0" customHeight="1">
-      <c r="A13" s="18" t="s">
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-    </row>
-    <row r="14" ht="12.0" customHeight="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19" t="s">
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-    </row>
-    <row r="15" ht="12.0" customHeight="1">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-    </row>
-    <row r="16" ht="12.0" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19" t="s">
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-    </row>
-    <row r="17" ht="12.0" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19" t="s">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="16"/>
+      <c r="D17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="19"/>
-    </row>
-    <row r="18" ht="12.0" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19" t="s">
+      <c r="E17" s="16"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-    </row>
-    <row r="19" ht="12.0" customHeight="1">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19" t="s">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="18">
         <v>-1.0E20</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-    </row>
-    <row r="20" ht="12.0" customHeight="1">
-      <c r="A20" s="19"/>
-      <c r="B20" s="22" t="s">
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16"/>
+      <c r="B20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-    </row>
-    <row r="21" ht="12.0" customHeight="1">
-      <c r="A21" s="19"/>
-      <c r="B21" s="22" t="s">
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16"/>
+      <c r="B21" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-    </row>
-    <row r="22" ht="12.0" customHeight="1">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19" t="s">
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-    </row>
-    <row r="23" ht="12.0" customHeight="1">
-      <c r="A23" s="24"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-    </row>
-    <row r="24" ht="12.0" customHeight="1">
-      <c r="A24" s="25" t="s">
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="20"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-    </row>
-    <row r="25" ht="12.0" customHeight="1">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19" t="s">
+      <c r="B24" s="16"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="16"/>
+      <c r="Z24" s="16"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-    </row>
-    <row r="26" ht="12.0" customHeight="1">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19" t="s">
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
+      <c r="T25" s="16"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="16"/>
+      <c r="X25" s="16"/>
+      <c r="Y25" s="16"/>
+      <c r="Z25" s="16"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
-      <c r="U26" s="19"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="19"/>
-      <c r="X26" s="19"/>
-      <c r="Y26" s="19"/>
-      <c r="Z26" s="19"/>
-    </row>
-    <row r="27" ht="12.0" customHeight="1">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19" t="s">
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="16"/>
+      <c r="Z26" s="16"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="17">
         <v>1.0</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="19"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="19"/>
-      <c r="X27" s="19"/>
-      <c r="Y27" s="19"/>
-      <c r="Z27" s="19"/>
-    </row>
-    <row r="28" ht="12.0" customHeight="1">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19" t="s">
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="16"/>
+      <c r="Z27" s="16"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="25" t="s">
+      <c r="C28" s="16"/>
+      <c r="D28" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="19"/>
-      <c r="Z28" s="19"/>
-    </row>
-    <row r="29" ht="12.0" customHeight="1">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19" t="s">
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="16"/>
+      <c r="Z28" s="16"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="19"/>
-      <c r="X29" s="19"/>
-      <c r="Y29" s="19"/>
-      <c r="Z29" s="19"/>
-    </row>
-    <row r="30" ht="12.0" customHeight="1">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19" t="s">
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="21">
-        <v>-1.0E10</v>
-      </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="19"/>
-      <c r="X30" s="19"/>
-      <c r="Y30" s="19"/>
-      <c r="Z30" s="19"/>
-    </row>
-    <row r="31" ht="12.0" customHeight="1">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19" t="s">
+      <c r="C30" s="19">
+        <v>-1.0E20</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="16"/>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="16"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="19"/>
-    </row>
-    <row r="32" ht="12.0" customHeight="1">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19" t="s">
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16"/>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="16"/>
+      <c r="Z31" s="16"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="19"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="19"/>
-      <c r="Z32" s="19"/>
-    </row>
-    <row r="33" ht="12.0" customHeight="1">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19" t="s">
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="16"/>
+      <c r="Z32" s="16"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="19"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="19"/>
-      <c r="Z33" s="19"/>
-    </row>
-    <row r="34" ht="12.0" customHeight="1">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19" t="s">
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
+      <c r="X33" s="16"/>
+      <c r="Y33" s="16"/>
+      <c r="Z33" s="16"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="19"/>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="19"/>
-      <c r="Z34" s="19"/>
-    </row>
-    <row r="35" ht="12.0" customHeight="1">
-      <c r="A35" s="24"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-    </row>
-    <row r="36" ht="12.0" customHeight="1">
-      <c r="A36" s="25" t="s">
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="20"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="20"/>
-    </row>
-    <row r="37" ht="12.0" customHeight="1">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19" t="s">
+      <c r="B36" s="16"/>
+      <c r="C36" s="17"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="12.0" customHeight="1">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19" t="s">
+    <row r="38">
+      <c r="A38" s="16"/>
+      <c r="B38" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" ht="12.0" customHeight="1">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19" t="s">
+    <row r="39">
+      <c r="A39" s="16"/>
+      <c r="B39" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="17">
         <v>1.0</v>
       </c>
     </row>
-    <row r="40" ht="12.0" customHeight="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="19" t="s">
+    <row r="40">
+      <c r="A40" s="16"/>
+      <c r="B40" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="25" t="s">
+      <c r="C40" s="16"/>
+      <c r="D40" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" ht="12.0" customHeight="1">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19" t="s">
+    <row r="41">
+      <c r="A41" s="16"/>
+      <c r="B41" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D41" s="25"/>
-    </row>
-    <row r="42" ht="12.0" customHeight="1">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19" t="s">
+      <c r="D41" s="16"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16"/>
+      <c r="B42" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="28">
-        <v>-1.0E10</v>
-      </c>
-    </row>
-    <row r="43" ht="12.0" customHeight="1">
-      <c r="B43" s="19" t="s">
+      <c r="C42" s="19">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="44" ht="12.0" customHeight="1">
-      <c r="B44" s="19" t="s">
+    <row r="44">
+      <c r="B44" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="27" t="s">
+      <c r="C44" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="45" ht="12.0" customHeight="1">
-      <c r="B45" s="19" t="s">
+    <row r="45">
+      <c r="B45" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="46" ht="12.0" customHeight="1">
-      <c r="B46" s="19" t="s">
+    <row r="46">
+      <c r="B46" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" ht="12.0" customHeight="1">
-      <c r="A47" s="24"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-    </row>
-    <row r="48" ht="12.0" customHeight="1">
-      <c r="A48" s="24" t="s">
+    <row r="47">
+      <c r="A47" s="20"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-    </row>
-    <row r="49" ht="12.0" customHeight="1">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22" t="s">
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="22" t="s">
+      <c r="C49" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="50" ht="12.0" customHeight="1">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22" t="s">
+    <row r="50">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" ht="12.0" customHeight="1">
-      <c r="A51" s="22"/>
-      <c r="B51" s="22" t="s">
+    <row r="51">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="52" ht="12.0" customHeight="1">
-      <c r="A52" s="22"/>
-      <c r="B52" s="22" t="s">
+    <row r="52">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="53" ht="12.0" customHeight="1">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22" t="s">
+    <row r="53">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C53" s="24" t="s">
+      <c r="C53" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="54" ht="12.0" customHeight="1">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22" t="s">
+    <row r="54">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C54" s="23">
+      <c r="C54" s="19">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="55" ht="12.0" customHeight="1">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22" t="s">
+    <row r="55">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="24"/>
-    </row>
-    <row r="56" ht="12.0" customHeight="1">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22" t="s">
+      <c r="E55" s="7"/>
+      <c r="F55" s="20"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="22"/>
-      <c r="F56" s="24"/>
-    </row>
-    <row r="57" ht="12.0" customHeight="1">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22" t="s">
+      <c r="E56" s="7"/>
+      <c r="F56" s="20"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="58" ht="12.0" customHeight="1">
-      <c r="A58" s="22"/>
-      <c r="B58" s="22" t="s">
+    <row r="58">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C58" s="22" t="s">
+      <c r="C58" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="59" ht="12.0" customHeight="1">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-    </row>
-    <row r="60" ht="12.0" customHeight="1">
-      <c r="A60" s="22" t="s">
+    <row r="59">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-    </row>
-    <row r="61" ht="12.0" customHeight="1">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22" t="s">
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7"/>
+      <c r="B61" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="C61" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="62" ht="12.0" customHeight="1">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22" t="s">
+    <row r="62">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" ht="12.0" customHeight="1">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22" t="s">
+    <row r="63">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="64" ht="12.0" customHeight="1">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22" t="s">
+    <row r="64">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65" ht="12.0" customHeight="1">
-      <c r="A65" s="22"/>
-      <c r="B65" s="22" t="s">
+    <row r="65">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C65" s="22" t="s">
+      <c r="C65" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="66" ht="12.0" customHeight="1">
-      <c r="A66" s="22"/>
-      <c r="B66" s="22" t="s">
+    <row r="66">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C66" s="23">
+      <c r="C66" s="19">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="67" ht="12.0" customHeight="1">
-      <c r="A67" s="22"/>
-      <c r="B67" s="22" t="s">
+    <row r="67">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="68" ht="12.0" customHeight="1">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22" t="s">
+    <row r="68">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="69" ht="12.0" customHeight="1">
-      <c r="A69" s="22"/>
-      <c r="B69" s="22" t="s">
+    <row r="69">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="70" ht="12.0" customHeight="1">
-      <c r="A70" s="22"/>
-      <c r="B70" s="22" t="s">
+    <row r="70">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="22" t="s">
+      <c r="C70" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="71" ht="12.0" customHeight="1">
-      <c r="C71" s="20"/>
-    </row>
-    <row r="72" ht="12.0" customHeight="1">
-      <c r="A72" s="22" t="s">
+    <row r="71">
+      <c r="C71" s="17"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22"/>
-    </row>
-    <row r="73" ht="12.0" customHeight="1">
-      <c r="A73" s="22"/>
-      <c r="B73" s="22" t="s">
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="74" ht="12.0" customHeight="1">
-      <c r="A74" s="22"/>
-      <c r="B74" s="22" t="s">
+    <row r="74">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="75" ht="12.0" customHeight="1">
-      <c r="A75" s="22"/>
-      <c r="B75" s="22" t="s">
+    <row r="75">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="76" ht="12.0" customHeight="1">
-      <c r="A76" s="22"/>
-      <c r="B76" s="22" t="s">
+    <row r="76">
+      <c r="A76" s="7"/>
+      <c r="B76" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C76" s="22"/>
-      <c r="D76" s="30" t="s">
+      <c r="C76" s="7"/>
+      <c r="D76" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="77" ht="12.0" customHeight="1">
-      <c r="A77" s="22"/>
-      <c r="B77" s="22" t="s">
+    <row r="77">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C77" s="22" t="s">
+      <c r="C77" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="78" ht="12.0" customHeight="1">
-      <c r="A78" s="22"/>
-      <c r="B78" s="22" t="s">
+    <row r="78">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C78" s="23">
+      <c r="C78" s="19">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="79" ht="12.0" customHeight="1">
-      <c r="A79" s="22"/>
-      <c r="B79" s="22" t="s">
+    <row r="79">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="80" ht="12.0" customHeight="1">
-      <c r="A80" s="22"/>
-      <c r="B80" s="22" t="s">
+    <row r="80">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="81" ht="12.0" customHeight="1">
-      <c r="A81" s="22"/>
-      <c r="B81" s="22" t="s">
+    <row r="81">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C81" s="22" t="s">
+      <c r="C81" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="82" ht="12.0" customHeight="1">
-      <c r="A82" s="22"/>
-      <c r="B82" s="22" t="s">
+    <row r="82">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C82" s="22" t="s">
+      <c r="C82" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="83" ht="12.0" customHeight="1">
-      <c r="C83" s="20"/>
-    </row>
-    <row r="84" ht="12.0" customHeight="1">
-      <c r="A84" s="22" t="s">
+    <row r="83">
+      <c r="C83" s="17"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B84" s="22"/>
-      <c r="C84" s="22"/>
-    </row>
-    <row r="85" ht="12.0" customHeight="1">
-      <c r="A85" s="22"/>
-      <c r="B85" s="22" t="s">
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C85" s="22" t="s">
+      <c r="C85" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="86" ht="12.0" customHeight="1">
-      <c r="A86" s="22"/>
-      <c r="B86" s="22" t="s">
+    <row r="86">
+      <c r="A86" s="7"/>
+      <c r="B86" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C86" s="22" t="s">
+      <c r="C86" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="87" ht="12.0" customHeight="1">
-      <c r="A87" s="22"/>
-      <c r="B87" s="22" t="s">
+    <row r="87">
+      <c r="A87" s="7"/>
+      <c r="B87" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C87" s="22" t="s">
+      <c r="C87" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="88" ht="12.0" customHeight="1">
-      <c r="A88" s="22"/>
-      <c r="B88" s="22" t="s">
+    <row r="88">
+      <c r="A88" s="7"/>
+      <c r="B88" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22" t="s">
+      <c r="C88" s="7"/>
+      <c r="D88" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="89" ht="12.0" customHeight="1">
-      <c r="A89" s="22"/>
-      <c r="B89" s="22" t="s">
+    <row r="89">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C89" s="22" t="s">
+      <c r="C89" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="90" ht="12.0" customHeight="1">
-      <c r="A90" s="22"/>
-      <c r="B90" s="22" t="s">
+    <row r="90">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C90" s="23">
+      <c r="C90" s="19">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="91" ht="12.0" customHeight="1">
-      <c r="A91" s="22"/>
-      <c r="B91" s="22" t="s">
+    <row r="91">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="92" ht="12.0" customHeight="1">
-      <c r="A92" s="22"/>
-      <c r="B92" s="22" t="s">
+    <row r="92">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C92" s="29" t="s">
+      <c r="C92" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="93" ht="12.0" customHeight="1">
-      <c r="A93" s="22"/>
-      <c r="B93" s="22" t="s">
+    <row r="93">
+      <c r="A93" s="7"/>
+      <c r="B93" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C93" s="22" t="s">
+      <c r="C93" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="94" ht="12.0" customHeight="1">
-      <c r="A94" s="22"/>
-      <c r="B94" s="22" t="s">
+    <row r="94">
+      <c r="A94" s="7"/>
+      <c r="B94" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C94" s="22" t="s">
+      <c r="C94" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="95" ht="12.0" customHeight="1">
-      <c r="C95" s="20"/>
-    </row>
-    <row r="96" ht="12.0" customHeight="1">
-      <c r="A96" s="22" t="s">
+    <row r="95">
+      <c r="C95" s="17"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22"/>
-    </row>
-    <row r="97" ht="12.0" customHeight="1">
-      <c r="A97" s="22"/>
-      <c r="B97" s="22" t="s">
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7"/>
+      <c r="B97" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C97" s="22" t="s">
+      <c r="C97" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="98" ht="12.0" customHeight="1">
-      <c r="A98" s="22"/>
-      <c r="B98" s="22" t="s">
+    <row r="98">
+      <c r="A98" s="7"/>
+      <c r="B98" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C98" s="22" t="s">
+      <c r="C98" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="99" ht="12.0" customHeight="1">
-      <c r="A99" s="22"/>
-      <c r="B99" s="22" t="s">
+    <row r="99">
+      <c r="A99" s="7"/>
+      <c r="B99" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C99" s="22" t="s">
+      <c r="C99" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="100" ht="12.0" customHeight="1">
-      <c r="A100" s="22"/>
-      <c r="B100" s="22" t="s">
+    <row r="100">
+      <c r="A100" s="7"/>
+      <c r="B100" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C100" s="22"/>
-      <c r="D100" s="22" t="s">
+      <c r="C100" s="7"/>
+      <c r="D100" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="101" ht="12.0" customHeight="1">
-      <c r="A101" s="22"/>
-      <c r="B101" s="22" t="s">
+    <row r="101">
+      <c r="A101" s="7"/>
+      <c r="B101" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C101" s="22" t="s">
+      <c r="C101" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="102" ht="12.0" customHeight="1">
-      <c r="A102" s="22"/>
-      <c r="B102" s="22" t="s">
+    <row r="102">
+      <c r="A102" s="7"/>
+      <c r="B102" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C102" s="23">
+      <c r="C102" s="19">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="103" ht="12.0" customHeight="1">
-      <c r="A103" s="22"/>
-      <c r="B103" s="22" t="s">
+    <row r="103">
+      <c r="A103" s="7"/>
+      <c r="B103" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C103" s="29" t="s">
+      <c r="C103" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="104" ht="12.0" customHeight="1">
-      <c r="A104" s="22"/>
-      <c r="B104" s="22" t="s">
+    <row r="104">
+      <c r="A104" s="7"/>
+      <c r="B104" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="105" ht="12.0" customHeight="1">
-      <c r="A105" s="22"/>
-      <c r="B105" s="22" t="s">
+    <row r="105">
+      <c r="A105" s="7"/>
+      <c r="B105" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C105" s="22" t="s">
+      <c r="C105" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="106" ht="12.0" customHeight="1">
-      <c r="A106" s="22"/>
-      <c r="B106" s="22" t="s">
+    <row r="106">
+      <c r="A106" s="7"/>
+      <c r="B106" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C106" s="22" t="s">
+      <c r="C106" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="107" ht="12.0" customHeight="1">
-      <c r="A107" s="22"/>
-      <c r="B107" s="22"/>
-      <c r="C107" s="22"/>
-    </row>
-    <row r="108" ht="12.0" customHeight="1">
-      <c r="A108" s="22" t="s">
+    <row r="107">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B108" s="22"/>
-      <c r="C108" s="22"/>
-    </row>
-    <row r="109" ht="12.0" customHeight="1">
-      <c r="B109" s="22" t="s">
+      <c r="B108" s="7"/>
+      <c r="C108" s="7"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C109" s="22" t="s">
+      <c r="C109" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="110" ht="12.0" customHeight="1">
-      <c r="A110" s="22"/>
-      <c r="B110" s="22" t="s">
+    <row r="110">
+      <c r="A110" s="7"/>
+      <c r="B110" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C110" s="22" t="s">
+      <c r="C110" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="111" ht="12.0" customHeight="1">
-      <c r="A111" s="22"/>
-      <c r="B111" s="22" t="s">
+    <row r="111">
+      <c r="A111" s="7"/>
+      <c r="B111" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C111" s="22" t="s">
+      <c r="C111" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E111" s="31"/>
-      <c r="F111" s="31"/>
-      <c r="G111" s="31"/>
-      <c r="H111" s="31"/>
-      <c r="I111" s="31"/>
-      <c r="J111" s="31"/>
-      <c r="K111" s="31"/>
-      <c r="L111" s="31"/>
-      <c r="M111" s="31"/>
-      <c r="N111" s="31"/>
-      <c r="O111" s="31"/>
-      <c r="P111" s="31"/>
-      <c r="Q111" s="31"/>
-      <c r="R111" s="31"/>
-      <c r="S111" s="31"/>
-      <c r="T111" s="31"/>
-      <c r="U111" s="31"/>
-      <c r="V111" s="31"/>
-      <c r="W111" s="31"/>
-      <c r="X111" s="31"/>
-      <c r="Y111" s="31"/>
-      <c r="Z111" s="31"/>
-    </row>
-    <row r="112" ht="12.0" customHeight="1">
-      <c r="A112" s="22"/>
-      <c r="B112" s="22" t="s">
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
+      <c r="I111" s="24"/>
+      <c r="J111" s="24"/>
+      <c r="K111" s="24"/>
+      <c r="L111" s="24"/>
+      <c r="M111" s="24"/>
+      <c r="N111" s="24"/>
+      <c r="O111" s="24"/>
+      <c r="P111" s="24"/>
+      <c r="Q111" s="24"/>
+      <c r="R111" s="24"/>
+      <c r="S111" s="24"/>
+      <c r="T111" s="24"/>
+      <c r="U111" s="24"/>
+      <c r="V111" s="24"/>
+      <c r="W111" s="24"/>
+      <c r="X111" s="24"/>
+      <c r="Y111" s="24"/>
+      <c r="Z111" s="24"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7"/>
+      <c r="B112" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C112" s="22"/>
-      <c r="D112" s="22" t="s">
+      <c r="C112" s="7"/>
+      <c r="D112" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="113" ht="12.0" customHeight="1">
-      <c r="A113" s="22"/>
-      <c r="B113" s="22" t="s">
+    <row r="113">
+      <c r="A113" s="7"/>
+      <c r="B113" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C113" s="22" t="s">
+      <c r="C113" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="114" ht="12.0" customHeight="1">
-      <c r="A114" s="22"/>
-      <c r="B114" s="22" t="s">
+    <row r="114">
+      <c r="A114" s="7"/>
+      <c r="B114" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C114" s="23">
+      <c r="C114" s="19">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="115" ht="12.0" customHeight="1">
-      <c r="A115" s="22"/>
-      <c r="B115" s="22" t="s">
+    <row r="115">
+      <c r="A115" s="7"/>
+      <c r="B115" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C115" s="29" t="s">
+      <c r="C115" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="116" ht="12.0" customHeight="1">
-      <c r="A116" s="22"/>
-      <c r="B116" s="22" t="s">
+    <row r="116">
+      <c r="A116" s="7"/>
+      <c r="B116" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C116" s="29" t="s">
+      <c r="C116" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="117" ht="12.0" customHeight="1">
-      <c r="A117" s="22"/>
-      <c r="B117" s="22" t="s">
+    <row r="117">
+      <c r="A117" s="7"/>
+      <c r="B117" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C117" s="22" t="s">
+      <c r="C117" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="118" ht="12.0" customHeight="1">
-      <c r="A118" s="22"/>
-      <c r="B118" s="22" t="s">
+    <row r="118">
+      <c r="A118" s="7"/>
+      <c r="B118" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C118" s="22" t="s">
+      <c r="C118" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="119" ht="12.0" customHeight="1">
-      <c r="C119" s="20"/>
-    </row>
-    <row r="120" ht="12.0" customHeight="1">
-      <c r="A120" s="22" t="s">
+    <row r="119">
+      <c r="C119" s="17"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B120" s="22"/>
-      <c r="C120" s="22"/>
-    </row>
-    <row r="121" ht="12.0" customHeight="1">
-      <c r="A121" s="22"/>
-      <c r="B121" s="22" t="s">
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7"/>
+      <c r="B121" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C121" s="22" t="s">
+      <c r="C121" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="122" ht="12.0" customHeight="1">
-      <c r="A122" s="22"/>
-      <c r="B122" s="22" t="s">
+    <row r="122">
+      <c r="A122" s="7"/>
+      <c r="B122" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C122" s="22" t="s">
+      <c r="C122" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="123" ht="12.0" customHeight="1">
-      <c r="A123" s="22"/>
-      <c r="B123" s="22" t="s">
+    <row r="123">
+      <c r="A123" s="7"/>
+      <c r="B123" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C123" s="22" t="s">
+      <c r="C123" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="124" ht="12.0" customHeight="1">
-      <c r="A124" s="22"/>
-      <c r="B124" s="22" t="s">
+    <row r="124">
+      <c r="A124" s="7"/>
+      <c r="B124" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C124" s="22"/>
-      <c r="D124" s="22" t="s">
+      <c r="C124" s="7"/>
+      <c r="D124" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="125" ht="12.0" customHeight="1">
-      <c r="A125" s="22"/>
-      <c r="B125" s="22" t="s">
+    <row r="125">
+      <c r="A125" s="7"/>
+      <c r="B125" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C125" s="22" t="s">
+      <c r="C125" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="126" ht="12.0" customHeight="1">
-      <c r="A126" s="22"/>
-      <c r="B126" s="22" t="s">
+    <row r="126">
+      <c r="A126" s="7"/>
+      <c r="B126" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C126" s="23">
+      <c r="C126" s="19">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="127" ht="12.0" customHeight="1">
-      <c r="A127" s="22"/>
-      <c r="B127" s="22" t="s">
+    <row r="127">
+      <c r="A127" s="7"/>
+      <c r="B127" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C127" s="29" t="s">
+      <c r="C127" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="128" ht="12.0" customHeight="1">
-      <c r="A128" s="22"/>
-      <c r="B128" s="22" t="s">
+    <row r="128">
+      <c r="A128" s="7"/>
+      <c r="B128" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C128" s="29" t="s">
+      <c r="C128" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="129" ht="12.0" customHeight="1">
-      <c r="A129" s="22"/>
-      <c r="B129" s="22" t="s">
+    <row r="129">
+      <c r="A129" s="7"/>
+      <c r="B129" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C129" s="22" t="s">
+      <c r="C129" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="130" ht="12.0" customHeight="1">
-      <c r="A130" s="22"/>
-      <c r="B130" s="22" t="s">
+    <row r="130">
+      <c r="A130" s="7"/>
+      <c r="B130" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C130" s="22" t="s">
+      <c r="C130" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="131" ht="12.0" customHeight="1">
-      <c r="C131" s="20"/>
-    </row>
-    <row r="132" ht="12.0" customHeight="1">
-      <c r="A132" s="18" t="s">
+    <row r="131">
+      <c r="C131" s="17"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="133" ht="12.0" customHeight="1">
-      <c r="B133" s="22" t="s">
+    <row r="133">
+      <c r="B133" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C133" s="32" t="s">
+      <c r="C133" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" s="7">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C136" s="7"/>
+      <c r="D136" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C138" s="19">
+        <v>-1.0E9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C139" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C140" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" s="17"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="12"/>
+      <c r="B145" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C145" s="17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="134" ht="12.0" customHeight="1">
-      <c r="B134" s="22" t="s">
+    <row r="146">
+      <c r="A146" s="12"/>
+      <c r="B146" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C134" s="22" t="s">
+      <c r="C146" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="135" ht="12.0" customHeight="1">
-      <c r="B135" s="22" t="s">
+    <row r="147">
+      <c r="A147" s="12"/>
+      <c r="B147" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C135" s="22">
+      <c r="C147" s="26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C148" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="24"/>
+      <c r="B149" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C149" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D149" s="24"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="12"/>
+      <c r="B150" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C150" s="18">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="12"/>
+      <c r="B151" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C151" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="12"/>
+      <c r="B152" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C152" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="12"/>
+      <c r="B153" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C153" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="12"/>
+      <c r="B154" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C154" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="C155" s="17"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B156" s="16"/>
+      <c r="C156" s="16"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="16"/>
+      <c r="B157" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C157" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="16"/>
+      <c r="B158" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C158" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="16"/>
+      <c r="B159" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C159" s="26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="16"/>
+      <c r="B160" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C160" s="17"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="16"/>
+      <c r="B161" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C161" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="16"/>
+      <c r="B162" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C162" s="18">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="16"/>
+      <c r="B163" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C163" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="16"/>
+      <c r="B164" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C164" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="16"/>
+      <c r="B165" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C165" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="16"/>
+      <c r="B166" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C166" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="K166" s="17"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="7"/>
+      <c r="B167" s="7"/>
+      <c r="C167" s="7"/>
+      <c r="K167" s="17"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B168" s="16"/>
+      <c r="C168" s="17"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="16"/>
+      <c r="B169" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C169" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="K169" s="26"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="16"/>
+      <c r="B170" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="K170" s="26"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="16"/>
+      <c r="B171" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" s="26">
         <v>1.0</v>
       </c>
-    </row>
-    <row r="136" ht="12.0" customHeight="1">
-      <c r="B136" s="22" t="s">
+      <c r="K171" s="17"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="16"/>
+      <c r="B172" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C136" s="22"/>
-      <c r="D136" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="137" ht="12.0" customHeight="1">
-      <c r="B137" s="22" t="s">
+      <c r="C172" s="26"/>
+      <c r="J172" s="7"/>
+      <c r="K172" s="28"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="16"/>
+      <c r="B173" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C137" s="22" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="138" ht="12.0" customHeight="1">
-      <c r="B138" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C138" s="23">
-        <v>-1.0E20</v>
-      </c>
-    </row>
-    <row r="139" ht="12.0" customHeight="1">
-      <c r="B139" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C139" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="140" ht="12.0" customHeight="1">
-      <c r="B140" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C140" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="141" ht="12.0" customHeight="1">
-      <c r="B141" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C141" s="22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="142" ht="12.0" customHeight="1">
-      <c r="B142" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C142" s="22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="143" ht="12.0" customHeight="1">
-      <c r="C143" s="20"/>
-    </row>
-    <row r="144" ht="12.0" customHeight="1">
-      <c r="A144" s="33" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="145" ht="12.0" customHeight="1">
-      <c r="A145" s="14"/>
-      <c r="B145" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C145" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="146" ht="12.0" customHeight="1">
-      <c r="A146" s="14"/>
-      <c r="B146" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="C146" s="20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="147" ht="12.0" customHeight="1">
-      <c r="A147" s="14"/>
-      <c r="B147" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="C147" s="35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="148" ht="12.0" customHeight="1">
-      <c r="B148" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C148" s="33" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="149" ht="12.0" customHeight="1">
-      <c r="A149" s="31"/>
-      <c r="B149" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C149" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D149" s="31"/>
-    </row>
-    <row r="150" ht="12.0" customHeight="1">
-      <c r="A150" s="14"/>
-      <c r="B150" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C150" s="21">
-        <v>-1.0E20</v>
-      </c>
-    </row>
-    <row r="151" ht="12.0" customHeight="1">
-      <c r="A151" s="14"/>
-      <c r="B151" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C151" s="27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="152" ht="12.0" customHeight="1">
-      <c r="A152" s="14"/>
-      <c r="B152" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="C152" s="27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="153" ht="12.0" customHeight="1">
-      <c r="A153" s="14"/>
-      <c r="B153" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C153" s="20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="154" ht="12.0" customHeight="1">
-      <c r="A154" s="14"/>
-      <c r="B154" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C154" s="20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="155" ht="12.0" customHeight="1">
-      <c r="C155" s="20"/>
-    </row>
-    <row r="156" ht="12.0" customHeight="1">
-      <c r="A156" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B156" s="19"/>
-      <c r="C156" s="19"/>
-    </row>
-    <row r="157" ht="12.0" customHeight="1">
-      <c r="A157" s="18"/>
-      <c r="B157" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C157" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="158" ht="12.0" customHeight="1">
-      <c r="A158" s="18"/>
-      <c r="B158" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C158" s="20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="159" ht="12.0" customHeight="1">
-      <c r="A159" s="18"/>
-      <c r="B159" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C159" s="35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="160" ht="12.0" customHeight="1">
-      <c r="A160" s="18"/>
-      <c r="B160" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C160" s="20"/>
-    </row>
-    <row r="161" ht="12.0" customHeight="1">
-      <c r="A161" s="18"/>
-      <c r="B161" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C161" s="36" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="162" ht="12.0" customHeight="1">
-      <c r="A162" s="18"/>
-      <c r="B162" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C162" s="21">
-        <v>-1.0E20</v>
-      </c>
-    </row>
-    <row r="163" ht="12.0" customHeight="1">
-      <c r="A163" s="18"/>
-      <c r="B163" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C163" s="27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="164" ht="12.0" customHeight="1">
-      <c r="A164" s="18"/>
-      <c r="B164" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C164" s="27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="165" ht="12.0" customHeight="1">
-      <c r="A165" s="18"/>
-      <c r="B165" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C165" s="20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="166" ht="12.0" customHeight="1">
-      <c r="A166" s="18"/>
-      <c r="B166" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C166" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="K166" s="20"/>
-    </row>
-    <row r="167" ht="12.0" customHeight="1">
-      <c r="A167" s="22"/>
-      <c r="B167" s="22"/>
-      <c r="C167" s="22"/>
-      <c r="K167" s="20"/>
-    </row>
-    <row r="168" ht="12.0" customHeight="1">
-      <c r="A168" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B168" s="19"/>
-      <c r="C168" s="20"/>
-    </row>
-    <row r="169" ht="12.0" customHeight="1">
-      <c r="A169" s="19"/>
-      <c r="B169" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C169" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="K169" s="35"/>
-    </row>
-    <row r="170" ht="12.0" customHeight="1">
-      <c r="A170" s="19"/>
-      <c r="B170" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="K170" s="35"/>
-    </row>
-    <row r="171" ht="12.0" customHeight="1">
-      <c r="A171" s="19"/>
-      <c r="B171" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C171" s="35">
-        <v>1.0</v>
-      </c>
-      <c r="K171" s="20"/>
-    </row>
-    <row r="172" ht="12.0" customHeight="1">
-      <c r="A172" s="19"/>
-      <c r="B172" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C172" s="35"/>
-      <c r="J172" s="22"/>
-      <c r="K172" s="37"/>
-    </row>
-    <row r="173" ht="12.0" customHeight="1">
-      <c r="A173" s="19"/>
-      <c r="B173" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C173" s="20" t="s">
-        <v>90</v>
+      <c r="C173" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
     </row>
-    <row r="174" ht="12.0" customHeight="1">
-      <c r="A174" s="19"/>
-      <c r="B174" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C174" s="37" t="s">
+    <row r="174">
+      <c r="A174" s="16"/>
+      <c r="B174" s="7" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="175" ht="12.0" customHeight="1">
-      <c r="A175" s="19"/>
+      <c r="C174" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="16"/>
       <c r="B175" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C175" s="4" t="s">
         <v>94</v>
       </c>
+      <c r="C175" s="29" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="176" ht="12.0" customHeight="1">
-      <c r="C176" s="27"/>
+      <c r="C176" s="21"/>
     </row>
     <row r="177" ht="12.0" customHeight="1">
-      <c r="C177" s="20"/>
+      <c r="C177" s="17"/>
     </row>
     <row r="178" ht="12.0" customHeight="1">
-      <c r="C178" s="20"/>
+      <c r="C178" s="17"/>
     </row>
     <row r="179" ht="12.0" customHeight="1"/>
     <row r="180" ht="12.0" customHeight="1">
-      <c r="C180" s="20"/>
+      <c r="C180" s="17"/>
     </row>
     <row r="181" ht="12.0" customHeight="1">
-      <c r="C181" s="20"/>
+      <c r="C181" s="17"/>
     </row>
     <row r="182" ht="12.0" customHeight="1">
-      <c r="C182" s="20"/>
+      <c r="C182" s="17"/>
     </row>
     <row r="183" ht="12.0" customHeight="1">
-      <c r="C183" s="20"/>
+      <c r="C183" s="17"/>
     </row>
     <row r="184" ht="12.0" customHeight="1">
-      <c r="C184" s="20"/>
+      <c r="C184" s="17"/>
     </row>
     <row r="185" ht="12.0" customHeight="1">
-      <c r="C185" s="20"/>
+      <c r="C185" s="17"/>
     </row>
     <row r="186" ht="12.0" customHeight="1">
-      <c r="C186" s="21"/>
+      <c r="C186" s="18"/>
     </row>
     <row r="187" ht="12.0" customHeight="1">
-      <c r="C187" s="27"/>
+      <c r="C187" s="21"/>
     </row>
     <row r="188" ht="12.0" customHeight="1">
-      <c r="C188" s="27"/>
+      <c r="C188" s="21"/>
     </row>
     <row r="189" ht="12.0" customHeight="1">
-      <c r="C189" s="20"/>
+      <c r="C189" s="17"/>
     </row>
     <row r="190" ht="12.0" customHeight="1">
-      <c r="C190" s="20"/>
+      <c r="C190" s="17"/>
     </row>
     <row r="191" ht="12.0" customHeight="1">
-      <c r="A191" s="22"/>
-      <c r="B191" s="22"/>
-      <c r="C191" s="22"/>
+      <c r="A191" s="7"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="7"/>
     </row>
     <row r="192" ht="12.0" customHeight="1">
-      <c r="A192" s="22"/>
-      <c r="B192" s="22"/>
-      <c r="C192" s="22"/>
+      <c r="A192" s="7"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
     </row>
     <row r="193" ht="12.0" customHeight="1">
-      <c r="A193" s="22"/>
-      <c r="B193" s="22"/>
-      <c r="C193" s="22"/>
+      <c r="A193" s="7"/>
+      <c r="B193" s="7"/>
+      <c r="C193" s="7"/>
     </row>
     <row r="194" ht="12.0" customHeight="1">
-      <c r="A194" s="22"/>
-      <c r="B194" s="22"/>
-      <c r="C194" s="22"/>
+      <c r="A194" s="7"/>
+      <c r="B194" s="7"/>
+      <c r="C194" s="7"/>
     </row>
     <row r="195" ht="12.0" customHeight="1">
-      <c r="A195" s="22"/>
-      <c r="B195" s="22"/>
-      <c r="C195" s="22"/>
+      <c r="A195" s="7"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="7"/>
     </row>
     <row r="196" ht="12.0" customHeight="1">
-      <c r="A196" s="22"/>
-      <c r="B196" s="22"/>
-      <c r="C196" s="23"/>
+      <c r="A196" s="7"/>
+      <c r="B196" s="7"/>
+      <c r="C196" s="19"/>
     </row>
     <row r="197" ht="12.0" customHeight="1">
-      <c r="A197" s="22"/>
-      <c r="B197" s="22"/>
-      <c r="C197" s="29"/>
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="22"/>
     </row>
     <row r="198" ht="12.0" customHeight="1">
-      <c r="A198" s="22"/>
-      <c r="B198" s="22"/>
-      <c r="C198" s="29"/>
+      <c r="A198" s="7"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="22"/>
     </row>
     <row r="199" ht="12.0" customHeight="1">
-      <c r="A199" s="22"/>
-      <c r="B199" s="22"/>
-      <c r="C199" s="22"/>
+      <c r="A199" s="7"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="7"/>
     </row>
     <row r="200" ht="12.0" customHeight="1">
-      <c r="A200" s="22"/>
-      <c r="B200" s="22"/>
-      <c r="C200" s="22"/>
+      <c r="A200" s="7"/>
+      <c r="B200" s="7"/>
+      <c r="C200" s="7"/>
     </row>
     <row r="201" ht="12.0" customHeight="1">
-      <c r="A201" s="22"/>
-      <c r="B201" s="22"/>
-      <c r="C201" s="22"/>
+      <c r="A201" s="7"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="7"/>
     </row>
     <row r="202" ht="12.0" customHeight="1">
-      <c r="A202" s="22"/>
-      <c r="B202" s="22"/>
-      <c r="C202" s="22"/>
+      <c r="A202" s="7"/>
+      <c r="B202" s="7"/>
+      <c r="C202" s="7"/>
     </row>
     <row r="203" ht="12.0" customHeight="1">
-      <c r="A203" s="22"/>
-      <c r="B203" s="22"/>
-      <c r="C203" s="22"/>
+      <c r="A203" s="7"/>
+      <c r="B203" s="7"/>
+      <c r="C203" s="7"/>
     </row>
     <row r="204" ht="12.0" customHeight="1">
-      <c r="A204" s="22"/>
-      <c r="B204" s="22"/>
-      <c r="C204" s="22"/>
+      <c r="A204" s="7"/>
+      <c r="B204" s="7"/>
+      <c r="C204" s="7"/>
     </row>
     <row r="205" ht="12.0" customHeight="1">
-      <c r="A205" s="22"/>
-      <c r="B205" s="22"/>
-      <c r="C205" s="22"/>
+      <c r="A205" s="7"/>
+      <c r="B205" s="7"/>
+      <c r="C205" s="7"/>
     </row>
     <row r="206" ht="12.0" customHeight="1">
-      <c r="A206" s="22"/>
-      <c r="B206" s="22"/>
-      <c r="C206" s="22"/>
+      <c r="A206" s="7"/>
+      <c r="B206" s="7"/>
+      <c r="C206" s="7"/>
     </row>
     <row r="207" ht="12.0" customHeight="1">
-      <c r="A207" s="22"/>
-      <c r="B207" s="22"/>
-      <c r="C207" s="22"/>
+      <c r="A207" s="7"/>
+      <c r="B207" s="7"/>
+      <c r="C207" s="7"/>
     </row>
     <row r="208" ht="12.0" customHeight="1">
-      <c r="A208" s="22"/>
-      <c r="B208" s="22"/>
-      <c r="C208" s="23"/>
+      <c r="A208" s="7"/>
+      <c r="B208" s="7"/>
+      <c r="C208" s="19"/>
     </row>
     <row r="209" ht="12.0" customHeight="1">
-      <c r="A209" s="22"/>
-      <c r="B209" s="22"/>
-      <c r="C209" s="29"/>
+      <c r="A209" s="7"/>
+      <c r="B209" s="7"/>
+      <c r="C209" s="22"/>
     </row>
     <row r="210" ht="12.0" customHeight="1">
-      <c r="A210" s="22"/>
-      <c r="B210" s="22"/>
-      <c r="C210" s="29"/>
+      <c r="A210" s="7"/>
+      <c r="B210" s="7"/>
+      <c r="C210" s="22"/>
     </row>
     <row r="211" ht="12.0" customHeight="1">
-      <c r="A211" s="22"/>
-      <c r="B211" s="22"/>
-      <c r="C211" s="22"/>
+      <c r="A211" s="7"/>
+      <c r="B211" s="7"/>
+      <c r="C211" s="7"/>
     </row>
     <row r="212" ht="12.0" customHeight="1">
-      <c r="A212" s="22"/>
-      <c r="B212" s="22"/>
-      <c r="C212" s="22"/>
+      <c r="A212" s="7"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="7"/>
     </row>
     <row r="213" ht="12.0" customHeight="1"/>
     <row r="214" ht="12.0" customHeight="1"/>
     <row r="215" ht="12.0" customHeight="1">
-      <c r="B215" s="22"/>
-      <c r="C215" s="22"/>
+      <c r="B215" s="7"/>
+      <c r="C215" s="7"/>
     </row>
     <row r="216" ht="12.0" customHeight="1">
-      <c r="B216" s="22"/>
-      <c r="C216" s="22"/>
+      <c r="B216" s="7"/>
+      <c r="C216" s="7"/>
     </row>
     <row r="217" ht="12.0" customHeight="1">
-      <c r="B217" s="22"/>
-      <c r="C217" s="22"/>
+      <c r="B217" s="7"/>
+      <c r="C217" s="7"/>
     </row>
     <row r="218" ht="12.0" customHeight="1">
-      <c r="B218" s="22"/>
-      <c r="C218" s="22"/>
+      <c r="B218" s="7"/>
+      <c r="C218" s="7"/>
     </row>
     <row r="219" ht="12.0" customHeight="1">
-      <c r="B219" s="22"/>
-      <c r="C219" s="22"/>
+      <c r="B219" s="7"/>
+      <c r="C219" s="7"/>
     </row>
     <row r="220" ht="12.0" customHeight="1">
-      <c r="B220" s="22"/>
-      <c r="C220" s="23"/>
+      <c r="B220" s="7"/>
+      <c r="C220" s="19"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="B221" s="22"/>
-      <c r="C221" s="29"/>
+      <c r="B221" s="7"/>
+      <c r="C221" s="22"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="B222" s="22"/>
-      <c r="C222" s="29"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="22"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="B223" s="22"/>
-      <c r="C223" s="22"/>
+      <c r="B223" s="7"/>
+      <c r="C223" s="7"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="B224" s="22"/>
-      <c r="C224" s="22"/>
+      <c r="B224" s="7"/>
+      <c r="C224" s="7"/>
     </row>
     <row r="225" ht="12.0" customHeight="1">
-      <c r="C225" s="20"/>
+      <c r="C225" s="17"/>
     </row>
     <row r="226" ht="12.0" customHeight="1">
-      <c r="C226" s="20"/>
+      <c r="C226" s="17"/>
     </row>
     <row r="227" ht="12.0" customHeight="1">
-      <c r="C227" s="20"/>
+      <c r="C227" s="17"/>
     </row>
     <row r="228" ht="12.0" customHeight="1"/>
     <row r="229" ht="12.0" customHeight="1">
-      <c r="C229" s="35"/>
+      <c r="C229" s="26"/>
     </row>
     <row r="230" ht="12.0" customHeight="1">
-      <c r="C230" s="35"/>
+      <c r="C230" s="26"/>
     </row>
     <row r="231" ht="12.0" customHeight="1">
-      <c r="C231" s="20"/>
+      <c r="C231" s="17"/>
     </row>
     <row r="232" ht="12.0" customHeight="1">
-      <c r="B232" s="22"/>
-      <c r="C232" s="37"/>
+      <c r="B232" s="7"/>
+      <c r="C232" s="28"/>
     </row>
     <row r="233" ht="12.0" customHeight="1">
       <c r="B233" s="4"/>
@@ -11576,18 +11563,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
-    <row r="1005" ht="15.75" customHeight="1"/>
-    <row r="1006" ht="15.75" customHeight="1"/>
-    <row r="1007" ht="15.75" customHeight="1"/>
-    <row r="1008" ht="15.75" customHeight="1"/>
-    <row r="1009" ht="15.75" customHeight="1"/>
-    <row r="1010" ht="15.75" customHeight="1"/>
-    <row r="1011" ht="15.75" customHeight="1"/>
-    <row r="1012" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/product-definitions/spreadsheet/precipitation.xlsx
+++ b/product-definitions/spreadsheet/precipitation.xlsx
@@ -388,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -405,7 +405,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="top"/>
@@ -465,9 +465,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8992,7 +8989,7 @@
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="16"/>
       <c r="B21" s="7" t="s">
         <v>45</v>
@@ -9003,7 +9000,7 @@
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="16"/>
       <c r="B22" s="16" t="s">
         <v>47</v>
@@ -9014,14 +9011,14 @@
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="20"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="16" t="s">
         <v>51</v>
       </c>
@@ -9051,7 +9048,7 @@
       <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="16"/>
       <c r="B25" s="16" t="s">
         <v>35</v>
@@ -9083,7 +9080,7 @@
       <c r="Y25" s="16"/>
       <c r="Z25" s="16"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="16"/>
       <c r="B26" s="16" t="s">
         <v>37</v>
@@ -9115,7 +9112,7 @@
       <c r="Y26" s="16"/>
       <c r="Z26" s="16"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="16"/>
       <c r="B27" s="16" t="s">
         <v>24</v>
@@ -9147,7 +9144,7 @@
       <c r="Y27" s="16"/>
       <c r="Z27" s="16"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="16"/>
       <c r="B28" s="16" t="s">
         <v>38</v>
@@ -9179,7 +9176,7 @@
       <c r="Y28" s="16"/>
       <c r="Z28" s="16"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="16"/>
       <c r="B29" s="16" t="s">
         <v>40</v>
@@ -9211,7 +9208,7 @@
       <c r="Y29" s="16"/>
       <c r="Z29" s="16"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="16"/>
       <c r="B30" s="16" t="s">
         <v>42</v>
@@ -9243,7 +9240,7 @@
       <c r="Y30" s="16"/>
       <c r="Z30" s="16"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="16"/>
       <c r="B31" s="16" t="s">
         <v>43</v>
@@ -9275,7 +9272,7 @@
       <c r="Y31" s="16"/>
       <c r="Z31" s="16"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="16"/>
       <c r="B32" s="16" t="s">
         <v>45</v>
@@ -9307,7 +9304,7 @@
       <c r="Y32" s="16"/>
       <c r="Z32" s="16"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="16"/>
       <c r="B33" s="16" t="s">
         <v>55</v>
@@ -9339,7 +9336,7 @@
       <c r="Y33" s="16"/>
       <c r="Z33" s="16"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="16"/>
       <c r="B34" s="16" t="s">
         <v>47</v>
@@ -9371,19 +9368,19 @@
       <c r="Y34" s="16"/>
       <c r="Z34" s="16"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="20"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="16" t="s">
         <v>57</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="17"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="16"/>
       <c r="B37" s="16" t="s">
         <v>35</v>
@@ -9392,7 +9389,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="16"/>
       <c r="B38" s="16" t="s">
         <v>37</v>
@@ -9401,7 +9398,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="16"/>
       <c r="B39" s="16" t="s">
         <v>24</v>
@@ -9410,7 +9407,7 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="16"/>
       <c r="B40" s="16" t="s">
         <v>38</v>
@@ -9420,7 +9417,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="16"/>
       <c r="B41" s="16" t="s">
         <v>40</v>
@@ -9430,7 +9427,7 @@
       </c>
       <c r="D41" s="16"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="16"/>
       <c r="B42" s="16" t="s">
         <v>42</v>
@@ -9439,7 +9436,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="16" t="s">
         <v>43</v>
       </c>
@@ -9447,7 +9444,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="16" t="s">
         <v>45</v>
       </c>
@@ -9455,7 +9452,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>55</v>
       </c>
@@ -9463,7 +9460,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="B46" s="16" t="s">
         <v>47</v>
       </c>
@@ -9471,19 +9468,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="20"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="20" t="s">
         <v>60</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="7"/>
       <c r="B49" s="7" t="s">
         <v>35</v>
@@ -9492,7 +9489,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7" t="s">
         <v>37</v>
@@ -9501,7 +9498,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
         <v>24</v>
@@ -9510,7 +9507,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="7"/>
       <c r="B52" s="7" t="s">
         <v>38</v>
@@ -9519,7 +9516,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="7"/>
       <c r="B53" s="7" t="s">
         <v>40</v>
@@ -9528,7 +9525,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="7"/>
       <c r="B54" s="7" t="s">
         <v>42</v>
@@ -9537,7 +9534,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="7"/>
       <c r="B55" s="7" t="s">
         <v>43</v>
@@ -9548,7 +9545,7 @@
       <c r="E55" s="7"/>
       <c r="F55" s="20"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="7"/>
       <c r="B56" s="7" t="s">
         <v>45</v>
@@ -9559,7 +9556,7 @@
       <c r="E56" s="7"/>
       <c r="F56" s="20"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="7"/>
       <c r="B57" s="7" t="s">
         <v>55</v>
@@ -9568,7 +9565,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="7"/>
       <c r="B58" s="7" t="s">
         <v>47</v>
@@ -9577,19 +9574,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="7" t="s">
         <v>64</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7"/>
       <c r="B61" s="7" t="s">
         <v>35</v>
@@ -9598,7 +9595,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="7"/>
       <c r="B62" s="7" t="s">
         <v>37</v>
@@ -9607,7 +9604,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="7"/>
       <c r="B63" s="7" t="s">
         <v>24</v>
@@ -9616,7 +9613,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="7"/>
       <c r="B64" s="7" t="s">
         <v>38</v>
@@ -9625,7 +9622,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="7"/>
       <c r="B65" s="7" t="s">
         <v>40</v>
@@ -9634,7 +9631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="7"/>
       <c r="B66" s="7" t="s">
         <v>42</v>
@@ -9643,7 +9640,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="7"/>
       <c r="B67" s="7" t="s">
         <v>43</v>
@@ -9652,7 +9649,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="7"/>
       <c r="B68" s="7" t="s">
         <v>45</v>
@@ -9661,7 +9658,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="7"/>
       <c r="B69" s="7" t="s">
         <v>55</v>
@@ -9670,7 +9667,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="7" t="s">
         <v>47</v>
@@ -9679,17 +9676,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="C71" s="17"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="7" t="s">
         <v>67</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="7"/>
       <c r="B73" s="7" t="s">
         <v>35</v>
@@ -9698,7 +9695,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="7"/>
       <c r="B74" s="7" t="s">
         <v>37</v>
@@ -9707,7 +9704,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="7"/>
       <c r="B75" s="7" t="s">
         <v>24</v>
@@ -9716,7 +9713,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="7"/>
       <c r="B76" s="7" t="s">
         <v>38</v>
@@ -9726,7 +9723,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="7"/>
       <c r="B77" s="7" t="s">
         <v>40</v>
@@ -9735,7 +9732,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="7"/>
       <c r="B78" s="7" t="s">
         <v>42</v>
@@ -9744,7 +9741,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="7"/>
       <c r="B79" s="7" t="s">
         <v>43</v>
@@ -9753,7 +9750,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="7" t="s">
         <v>45</v>
@@ -9762,7 +9759,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="7"/>
       <c r="B81" s="7" t="s">
         <v>55</v>
@@ -9771,7 +9768,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
         <v>47</v>
@@ -9780,17 +9777,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="C83" s="17"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="7" t="s">
         <v>69</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="7"/>
       <c r="B85" s="7" t="s">
         <v>35</v>
@@ -9799,7 +9796,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="7"/>
       <c r="B86" s="7" t="s">
         <v>37</v>
@@ -9808,7 +9805,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="7"/>
       <c r="B87" s="7" t="s">
         <v>24</v>
@@ -9817,7 +9814,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="7"/>
       <c r="B88" s="7" t="s">
         <v>38</v>
@@ -9827,7 +9824,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="7"/>
       <c r="B89" s="7" t="s">
         <v>40</v>
@@ -9836,7 +9833,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7" t="s">
         <v>42</v>
@@ -9845,7 +9842,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="7"/>
       <c r="B91" s="7" t="s">
         <v>43</v>
@@ -9854,7 +9851,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="7"/>
       <c r="B92" s="7" t="s">
         <v>45</v>
@@ -9863,7 +9860,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="7"/>
       <c r="B93" s="7" t="s">
         <v>55</v>
@@ -9872,7 +9869,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="7"/>
       <c r="B94" s="7" t="s">
         <v>47</v>
@@ -9881,17 +9878,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="C95" s="17"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="7" t="s">
         <v>71</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="7"/>
       <c r="B97" s="7" t="s">
         <v>35</v>
@@ -9900,7 +9897,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="7"/>
       <c r="B98" s="7" t="s">
         <v>37</v>
@@ -9909,7 +9906,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="7"/>
       <c r="B99" s="7" t="s">
         <v>24</v>
@@ -9918,7 +9915,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="7"/>
       <c r="B100" s="7" t="s">
         <v>38</v>
@@ -9928,7 +9925,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="7"/>
       <c r="B101" s="7" t="s">
         <v>40</v>
@@ -9937,7 +9934,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="7"/>
       <c r="B102" s="7" t="s">
         <v>42</v>
@@ -9946,7 +9943,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="7"/>
       <c r="B103" s="7" t="s">
         <v>43</v>
@@ -9955,7 +9952,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="7"/>
       <c r="B104" s="7" t="s">
         <v>45</v>
@@ -9964,7 +9961,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="7"/>
       <c r="B105" s="7" t="s">
         <v>55</v>
@@ -9973,7 +9970,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="7"/>
       <c r="B106" s="7" t="s">
         <v>47</v>
@@ -9982,19 +9979,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="7" t="s">
         <v>74</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="B109" s="7" t="s">
         <v>35</v>
       </c>
@@ -10002,7 +9999,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="7"/>
       <c r="B110" s="7" t="s">
         <v>37</v>
@@ -10011,7 +10008,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="7"/>
       <c r="B111" s="7" t="s">
         <v>24</v>
@@ -10042,7 +10039,7 @@
       <c r="Y111" s="24"/>
       <c r="Z111" s="24"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="7"/>
       <c r="B112" s="7" t="s">
         <v>38</v>
@@ -10052,7 +10049,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="7"/>
       <c r="B113" s="7" t="s">
         <v>40</v>
@@ -10061,7 +10058,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="7"/>
       <c r="B114" s="7" t="s">
         <v>42</v>
@@ -10070,7 +10067,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="7"/>
       <c r="B115" s="7" t="s">
         <v>43</v>
@@ -10079,7 +10076,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="7"/>
       <c r="B116" s="7" t="s">
         <v>45</v>
@@ -10088,7 +10085,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="7"/>
       <c r="B117" s="7" t="s">
         <v>55</v>
@@ -10097,7 +10094,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="7"/>
       <c r="B118" s="7" t="s">
         <v>47</v>
@@ -10106,17 +10103,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="C119" s="17"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="7" t="s">
         <v>77</v>
       </c>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="7"/>
       <c r="B121" s="7" t="s">
         <v>35</v>
@@ -10125,7 +10122,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="7"/>
       <c r="B122" s="7" t="s">
         <v>37</v>
@@ -10134,7 +10131,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="7"/>
       <c r="B123" s="7" t="s">
         <v>24</v>
@@ -10143,7 +10140,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="7"/>
       <c r="B124" s="7" t="s">
         <v>38</v>
@@ -10153,7 +10150,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="7"/>
       <c r="B125" s="7" t="s">
         <v>40</v>
@@ -10162,7 +10159,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="7"/>
       <c r="B126" s="7" t="s">
         <v>42</v>
@@ -10171,7 +10168,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="7"/>
       <c r="B127" s="7" t="s">
         <v>43</v>
@@ -10180,7 +10177,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="7"/>
       <c r="B128" s="7" t="s">
         <v>45</v>
@@ -10189,7 +10186,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="7"/>
       <c r="B129" s="7" t="s">
         <v>55</v>
@@ -10198,7 +10195,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="7"/>
       <c r="B130" s="7" t="s">
         <v>47</v>
@@ -10207,15 +10204,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="C131" s="17"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="16" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="B133" s="7" t="s">
         <v>35</v>
       </c>
@@ -10223,7 +10220,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="B134" s="7" t="s">
         <v>37</v>
       </c>
@@ -10231,7 +10228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="7" t="s">
         <v>24</v>
       </c>
@@ -10239,7 +10236,7 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="B136" s="7" t="s">
         <v>38</v>
       </c>
@@ -10248,7 +10245,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="B137" s="7" t="s">
         <v>40</v>
       </c>
@@ -10256,7 +10253,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="B138" s="7" t="s">
         <v>42</v>
       </c>
@@ -10264,7 +10261,7 @@
         <v>-1.0E9</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="B139" s="7" t="s">
         <v>43</v>
       </c>
@@ -10272,7 +10269,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="B140" s="7" t="s">
         <v>45</v>
       </c>
@@ -10280,7 +10277,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="B141" s="7" t="s">
         <v>55</v>
       </c>
@@ -10288,7 +10285,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="B142" s="7" t="s">
         <v>47</v>
       </c>
@@ -10296,15 +10293,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="C143" s="17"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="12"/>
       <c r="B145" s="12" t="s">
         <v>35</v>
@@ -10313,7 +10310,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="12"/>
       <c r="B146" s="12" t="s">
         <v>37</v>
@@ -10322,7 +10319,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="12"/>
       <c r="B147" s="12" t="s">
         <v>24</v>
@@ -10331,7 +10328,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="B148" s="12" t="s">
         <v>38</v>
       </c>
@@ -10339,7 +10336,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="24"/>
       <c r="B149" s="24" t="s">
         <v>40</v>
@@ -10349,7 +10346,7 @@
       </c>
       <c r="D149" s="24"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="12"/>
       <c r="B150" s="12" t="s">
         <v>42</v>
@@ -10358,7 +10355,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="12"/>
       <c r="B151" s="12" t="s">
         <v>43</v>
@@ -10367,7 +10364,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="12"/>
       <c r="B152" s="12" t="s">
         <v>45</v>
@@ -10376,7 +10373,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="12"/>
       <c r="B153" s="12" t="s">
         <v>55</v>
@@ -10385,7 +10382,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="12"/>
       <c r="B154" s="12" t="s">
         <v>47</v>
@@ -10394,17 +10391,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="C155" s="17"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="16" t="s">
         <v>86</v>
       </c>
       <c r="B156" s="16"/>
       <c r="C156" s="16"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="16"/>
       <c r="B157" s="16" t="s">
         <v>35</v>
@@ -10413,7 +10410,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="16"/>
       <c r="B158" s="16" t="s">
         <v>37</v>
@@ -10422,7 +10419,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="16"/>
       <c r="B159" s="16" t="s">
         <v>24</v>
@@ -10431,14 +10428,14 @@
         <v>87</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="16"/>
       <c r="B160" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C160" s="17"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="16"/>
       <c r="B161" s="16" t="s">
         <v>40</v>
@@ -10447,7 +10444,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="16"/>
       <c r="B162" s="16" t="s">
         <v>42</v>
@@ -10456,7 +10453,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="16"/>
       <c r="B163" s="16" t="s">
         <v>43</v>
@@ -10465,7 +10462,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="16"/>
       <c r="B164" s="16" t="s">
         <v>45</v>
@@ -10474,7 +10471,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="16"/>
       <c r="B165" s="16" t="s">
         <v>55</v>
@@ -10483,7 +10480,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="16"/>
       <c r="B166" s="16" t="s">
         <v>47</v>
@@ -10493,20 +10490,20 @@
       </c>
       <c r="K166" s="17"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
       <c r="K167" s="17"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="16" t="s">
         <v>89</v>
       </c>
       <c r="B168" s="16"/>
       <c r="C168" s="17"/>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="16"/>
       <c r="B169" s="16" t="s">
         <v>35</v>
@@ -10516,7 +10513,7 @@
       </c>
       <c r="K169" s="26"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="16"/>
       <c r="B170" s="16" t="s">
         <v>37</v>
@@ -10526,7 +10523,7 @@
       </c>
       <c r="K170" s="26"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="16"/>
       <c r="B171" s="16" t="s">
         <v>24</v>
@@ -10536,7 +10533,7 @@
       </c>
       <c r="K171" s="17"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="16"/>
       <c r="B172" s="16" t="s">
         <v>38</v>
@@ -10545,7 +10542,7 @@
       <c r="J172" s="7"/>
       <c r="K172" s="28"/>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="16"/>
       <c r="B173" s="16" t="s">
         <v>40</v>
@@ -10556,7 +10553,7 @@
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="16"/>
       <c r="B174" s="7" t="s">
         <v>92</v>
@@ -10565,12 +10562,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="16"/>
       <c r="B175" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C175" s="29" t="s">
+      <c r="C175" s="4" t="s">
         <v>95</v>
       </c>
     </row>
